--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty200 Value 30 ETF.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty200 Value 30 ETF.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\mumchfnp01\RatingFinance\Factseet Mandates\ICICI PRUDENTIAL FACTSHEET\2025\Feb\Portfolio stage 8\Riskometer updated Portfolio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\mumchfnp01\RatingFinance\Factseet Mandates\ICICI PRUDENTIAL FACTSHEET\2025\June\Portfolio stage 8\Riskometer updated portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4BA63A3-3B74-49A1-9BE9-1EA6DF4B0C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E222BD5-B4F2-4354-A099-6FF7B4B31930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="113">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -28,7 +28,7 @@
     <t>ICICI Prudential Nifty200 Value 30 ETF</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -67,6 +67,66 @@
     <t>Listed / Awaiting Listing On Stock Exchanges</t>
   </si>
   <si>
+    <t>Tata Steel Ltd.</t>
+  </si>
+  <si>
+    <t>INE081A01020</t>
+  </si>
+  <si>
+    <t>Ferrous Metals</t>
+  </si>
+  <si>
+    <t>Bharat Petroleum Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE029A01011</t>
+  </si>
+  <si>
+    <t>Petroleum Products</t>
+  </si>
+  <si>
+    <t>Indian Oil Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE242A01010</t>
+  </si>
+  <si>
+    <t>Coal India Ltd.</t>
+  </si>
+  <si>
+    <t>INE522F01014</t>
+  </si>
+  <si>
+    <t>Consumable Fuels</t>
+  </si>
+  <si>
+    <t>Hindalco Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE038A01020</t>
+  </si>
+  <si>
+    <t>Non - Ferrous Metals</t>
+  </si>
+  <si>
+    <t>State Bank Of India</t>
+  </si>
+  <si>
+    <t>INE062A01020</t>
+  </si>
+  <si>
+    <t>Banks</t>
+  </si>
+  <si>
+    <t>NTPC Ltd.</t>
+  </si>
+  <si>
+    <t>INE733E01010</t>
+  </si>
+  <si>
+    <t>Power</t>
+  </si>
+  <si>
     <t>Oil &amp; Natural Gas Corporation Ltd.</t>
   </si>
   <si>
@@ -76,13 +136,28 @@
     <t>Oil</t>
   </si>
   <si>
-    <t>Coal India Ltd.</t>
-  </si>
-  <si>
-    <t>INE522F01014</t>
-  </si>
-  <si>
-    <t>Consumable Fuels</t>
+    <t>Hindustan Petroleum Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE094A01015</t>
+  </si>
+  <si>
+    <t>Grasim Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE047A01021</t>
+  </si>
+  <si>
+    <t>Cement &amp; Cement Products</t>
+  </si>
+  <si>
+    <t>Vedanta Ltd.</t>
+  </si>
+  <si>
+    <t>INE205A01025</t>
+  </si>
+  <si>
+    <t>Diversified Metals</t>
   </si>
   <si>
     <t>Power Grid Corporation Of India Ltd.</t>
@@ -91,69 +166,6 @@
     <t>INE752E01010</t>
   </si>
   <si>
-    <t>Power</t>
-  </si>
-  <si>
-    <t>NTPC Ltd.</t>
-  </si>
-  <si>
-    <t>INE733E01010</t>
-  </si>
-  <si>
-    <t>Tata Steel Ltd.</t>
-  </si>
-  <si>
-    <t>INE081A01020</t>
-  </si>
-  <si>
-    <t>Ferrous Metals</t>
-  </si>
-  <si>
-    <t>Vedanta Ltd.</t>
-  </si>
-  <si>
-    <t>INE205A01025</t>
-  </si>
-  <si>
-    <t>Diversified Metals</t>
-  </si>
-  <si>
-    <t>State Bank Of India</t>
-  </si>
-  <si>
-    <t>INE062A01020</t>
-  </si>
-  <si>
-    <t>Banks</t>
-  </si>
-  <si>
-    <t>Hindalco Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE038A01020</t>
-  </si>
-  <si>
-    <t>Non - Ferrous Metals</t>
-  </si>
-  <si>
-    <t>Grasim Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE047A01021</t>
-  </si>
-  <si>
-    <t>Cement &amp; Cement Products</t>
-  </si>
-  <si>
-    <t>Indian Oil Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE242A01010</t>
-  </si>
-  <si>
-    <t>Petroleum Products</t>
-  </si>
-  <si>
     <t>Power Finance Corporation Ltd.</t>
   </si>
   <si>
@@ -163,18 +175,6 @@
     <t>Finance</t>
   </si>
   <si>
-    <t>Bharat Petroleum Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE029A01011</t>
-  </si>
-  <si>
-    <t>Hindustan Petroleum Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE094A01015</t>
-  </si>
-  <si>
     <t>Bank Of Baroda</t>
   </si>
   <si>
@@ -187,25 +187,31 @@
     <t>INE721A01047</t>
   </si>
   <si>
+    <t>Canara Bank</t>
+  </si>
+  <si>
+    <t>INE476A01022</t>
+  </si>
+  <si>
+    <t>GAIL (India) Ltd.</t>
+  </si>
+  <si>
+    <t>INE129A01019</t>
+  </si>
+  <si>
+    <t>Gas</t>
+  </si>
+  <si>
     <t>Rural Electrification Corporation Ltd.</t>
   </si>
   <si>
     <t>INE020B01018</t>
   </si>
   <si>
-    <t>GAIL (India) Ltd.</t>
-  </si>
-  <si>
-    <t>INE129A01019</t>
-  </si>
-  <si>
-    <t>Gas</t>
-  </si>
-  <si>
-    <t>Canara Bank</t>
-  </si>
-  <si>
-    <t>INE476A01022</t>
+    <t>Union Bank Of India</t>
+  </si>
+  <si>
+    <t>INE692A01016</t>
   </si>
   <si>
     <t>Punjab National Bank</t>
@@ -214,12 +220,6 @@
     <t>INE160A01022</t>
   </si>
   <si>
-    <t>Union Bank Of India</t>
-  </si>
-  <si>
-    <t>INE692A01016</t>
-  </si>
-  <si>
     <t>The Federal Bank Ltd.</t>
   </si>
   <si>
@@ -235,31 +235,37 @@
     <t>Fertilizers &amp; Agrochemicals</t>
   </si>
   <si>
+    <t>Steel Authority Of India Ltd.</t>
+  </si>
+  <si>
+    <t>INE114A01011</t>
+  </si>
+  <si>
+    <t>NMDC Ltd.</t>
+  </si>
+  <si>
+    <t>INE584A01023</t>
+  </si>
+  <si>
+    <t>Minerals &amp; Mining</t>
+  </si>
+  <si>
+    <t>Indian Bank</t>
+  </si>
+  <si>
+    <t>INE562A01011</t>
+  </si>
+  <si>
     <t>Petronet LNG Ltd.</t>
   </si>
   <si>
     <t>INE347G01014</t>
   </si>
   <si>
-    <t>NMDC Ltd.</t>
-  </si>
-  <si>
-    <t>INE584A01023</t>
-  </si>
-  <si>
-    <t>Minerals &amp; Mining</t>
-  </si>
-  <si>
-    <t>Indian Bank</t>
-  </si>
-  <si>
-    <t>INE562A01011</t>
-  </si>
-  <si>
-    <t>Steel Authority Of India Ltd.</t>
-  </si>
-  <si>
-    <t>INE114A01011</t>
+    <t>Bank Of India</t>
+  </si>
+  <si>
+    <t>INE084A01016</t>
   </si>
   <si>
     <t>LIC Housing Finance Ltd.</t>
@@ -268,10 +274,10 @@
     <t>INE115A01026</t>
   </si>
   <si>
-    <t>Bank Of India</t>
-  </si>
-  <si>
-    <t>INE084A01016</t>
+    <t>Indraprastha Gas Ltd.</t>
+  </si>
+  <si>
+    <t>INE203G01027</t>
   </si>
   <si>
     <t>Tata Chemicals Ltd.</t>
@@ -283,12 +289,6 @@
     <t>Chemicals &amp; Petrochemicals</t>
   </si>
   <si>
-    <t>Indraprastha Gas Ltd.</t>
-  </si>
-  <si>
-    <t>INE203G01027</t>
-  </si>
-  <si>
     <t>Unlisted</t>
   </si>
   <si>
@@ -331,9 +331,6 @@
     <t>TREPS</t>
   </si>
   <si>
-    <t>^</t>
-  </si>
-  <si>
     <t>Net Current Assets</t>
   </si>
   <si>
@@ -343,16 +340,13 @@
     <t>Non-Convertible debentures / Bonds &amp; Zero Coupon Bonds / Deep Discount Bonds / Certificate of Deposits / Commercial Papers are considered as Traded based on the information provided by external agencies.</t>
   </si>
   <si>
-    <t>^ Value Less than 0.01% of NAV in absolute terms.</t>
-  </si>
-  <si>
     <t>For the Instrument/security whose final ISIN is yet to be assigned, disclosure of ISIN has been made as per the details provided by external agencies.</t>
   </si>
   <si>
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -567,6 +561,7 @@
   </cellStyleXfs>
   <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
@@ -579,14 +574,13 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
@@ -663,13 +657,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>81</xdr:row>
+      <xdr:row>80</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>91</xdr:row>
+      <xdr:row>90</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -693,7 +687,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="15887700"/>
+          <a:off x="666750" y="15697200"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -710,13 +704,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>96</xdr:row>
+      <xdr:row>95</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>106</xdr:row>
+      <xdr:row>105</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -740,7 +734,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="18745200"/>
+          <a:off x="666750" y="18554700"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1076,7 +1070,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J95"/>
+  <dimension ref="A1:J94"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" style="24" customWidth="1" collapsed="1"/>
@@ -1092,43 +1086,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
     </row>
     <row r="2" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
     </row>
     <row r="3" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
     </row>
     <row r="4" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="7" t="s">
@@ -1176,10 +1170,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="12">
-        <v>870.26</v>
+        <v>1022.25</v>
       </c>
       <c r="H5" s="13">
-        <v>0.99770745133989991</v>
+        <v>0.9999738355572001</v>
       </c>
       <c r="I5" s="12" t="s">
         <v>13</v>
@@ -1213,10 +1207,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="12">
-        <v>870.26</v>
+        <v>1022.25</v>
       </c>
       <c r="H7" s="13">
-        <v>0.99770745133989991</v>
+        <v>0.9999738355572001</v>
       </c>
       <c r="I7" s="12" t="s">
         <v>13</v>
@@ -1239,13 +1233,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="17">
-        <v>19018</v>
+        <v>35965</v>
       </c>
       <c r="G8" s="18">
-        <v>49.94</v>
+        <v>57.91</v>
       </c>
       <c r="H8" s="19">
-        <v>5.7253591018699999E-2</v>
+        <v>5.6648065362800003E-2</v>
       </c>
       <c r="I8" s="18" t="s">
         <v>13</v>
@@ -1268,13 +1262,13 @@
         <v>20</v>
       </c>
       <c r="F9" s="17">
-        <v>11817</v>
+        <v>17077</v>
       </c>
       <c r="G9" s="18">
-        <v>46.78</v>
+        <v>54.37</v>
       </c>
       <c r="H9" s="19">
-        <v>5.36308167372E-2</v>
+        <v>5.3185206592600003E-2</v>
       </c>
       <c r="I9" s="18" t="s">
         <v>13</v>
@@ -1294,16 +1288,16 @@
         <v>13</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F10" s="17">
-        <v>14726</v>
+        <v>36620</v>
       </c>
       <c r="G10" s="18">
-        <v>44.42</v>
+        <v>51.99</v>
       </c>
       <c r="H10" s="19">
-        <v>5.0925200501600001E-2</v>
+        <v>5.0857069905299999E-2</v>
       </c>
       <c r="I10" s="18" t="s">
         <v>13</v>
@@ -1314,25 +1308,25 @@
     </row>
     <row r="11" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="D11" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="16" t="s">
-        <v>23</v>
-      </c>
       <c r="F11" s="17">
-        <v>13653</v>
+        <v>13057</v>
       </c>
       <c r="G11" s="18">
-        <v>44.24</v>
+        <v>51.88</v>
       </c>
       <c r="H11" s="19">
-        <v>5.0718839941299998E-2</v>
+        <v>5.07494669491E-2</v>
       </c>
       <c r="I11" s="18" t="s">
         <v>13</v>
@@ -1355,13 +1349,13 @@
         <v>28</v>
       </c>
       <c r="F12" s="17">
-        <v>32557</v>
+        <v>8028</v>
       </c>
       <c r="G12" s="18">
-        <v>43.83</v>
+        <v>50.86</v>
       </c>
       <c r="H12" s="19">
-        <v>5.02487964427E-2</v>
+        <v>4.9751694083099998E-2</v>
       </c>
       <c r="I12" s="18" t="s">
         <v>13</v>
@@ -1384,13 +1378,13 @@
         <v>31</v>
       </c>
       <c r="F13" s="17">
-        <v>9923</v>
+        <v>6213</v>
       </c>
       <c r="G13" s="18">
-        <v>43.8</v>
+        <v>50.47</v>
       </c>
       <c r="H13" s="19">
-        <v>5.0214403015999998E-2</v>
+        <v>4.9370192693199998E-2</v>
       </c>
       <c r="I13" s="18" t="s">
         <v>13</v>
@@ -1413,13 +1407,13 @@
         <v>34</v>
       </c>
       <c r="F14" s="17">
-        <v>5623</v>
+        <v>15084</v>
       </c>
       <c r="G14" s="18">
-        <v>43.46</v>
+        <v>50.37</v>
       </c>
       <c r="H14" s="19">
-        <v>4.98246108465E-2</v>
+        <v>4.9272371824000002E-2</v>
       </c>
       <c r="I14" s="18" t="s">
         <v>13</v>
@@ -1442,13 +1436,13 @@
         <v>37</v>
       </c>
       <c r="F15" s="17">
-        <v>7268</v>
+        <v>21012</v>
       </c>
       <c r="G15" s="18">
-        <v>43.19</v>
+        <v>50.3</v>
       </c>
       <c r="H15" s="19">
-        <v>4.9515070006E-2</v>
+        <v>4.9203897215500003E-2</v>
       </c>
       <c r="I15" s="18" t="s">
         <v>13</v>
@@ -1468,16 +1462,16 @@
         <v>13</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F16" s="17">
-        <v>1707</v>
+        <v>12039</v>
       </c>
       <c r="G16" s="18">
-        <v>42.83</v>
+        <v>49.49</v>
       </c>
       <c r="H16" s="19">
-        <v>4.9102348885299997E-2</v>
+        <v>4.8411548174900003E-2</v>
       </c>
       <c r="I16" s="18" t="s">
         <v>13</v>
@@ -1488,25 +1482,25 @@
     </row>
     <row r="17" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="D17" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="D17" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" s="16" t="s">
-        <v>43</v>
-      </c>
       <c r="F17" s="17">
-        <v>33149</v>
+        <v>1888</v>
       </c>
       <c r="G17" s="18">
-        <v>42.59</v>
+        <v>48.06</v>
       </c>
       <c r="H17" s="19">
-        <v>4.8827201471499999E-2</v>
+        <v>4.7012709745100002E-2</v>
       </c>
       <c r="I17" s="18" t="s">
         <v>13</v>
@@ -1517,25 +1511,25 @@
     </row>
     <row r="18" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="D18" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="D18" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18" s="16" t="s">
-        <v>46</v>
-      </c>
       <c r="F18" s="17">
-        <v>9865</v>
+        <v>10963</v>
       </c>
       <c r="G18" s="18">
-        <v>41.68</v>
+        <v>47.75</v>
       </c>
       <c r="H18" s="19">
-        <v>4.7783934194200003E-2</v>
+        <v>4.6709465050499999E-2</v>
       </c>
       <c r="I18" s="18" t="s">
         <v>13</v>
@@ -1546,25 +1540,25 @@
     </row>
     <row r="19" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="16" t="s">
-        <v>48</v>
-      </c>
       <c r="D19" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="F19" s="17">
-        <v>15459</v>
+        <v>16268</v>
       </c>
       <c r="G19" s="18">
-        <v>40.36</v>
+        <v>47.14</v>
       </c>
       <c r="H19" s="19">
-        <v>4.6270623418399999E-2</v>
+        <v>4.6112757748300003E-2</v>
       </c>
       <c r="I19" s="18" t="s">
         <v>13</v>
@@ -1575,25 +1569,25 @@
     </row>
     <row r="20" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="D20" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="16" t="s">
         <v>50</v>
-      </c>
-      <c r="D20" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20" s="16" t="s">
-        <v>43</v>
       </c>
       <c r="F20" s="17">
         <v>10897</v>
       </c>
       <c r="G20" s="18">
-        <v>39.04</v>
+        <v>44.24</v>
       </c>
       <c r="H20" s="19">
-        <v>4.4757312642600001E-2</v>
+        <v>4.3275952541000001E-2</v>
       </c>
       <c r="I20" s="18" t="s">
         <v>13</v>
@@ -1613,16 +1607,16 @@
         <v>13</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F21" s="17">
-        <v>14836</v>
+        <v>16390</v>
       </c>
       <c r="G21" s="18">
-        <v>31.66</v>
+        <v>40.9</v>
       </c>
       <c r="H21" s="19">
-        <v>3.6296529668600003E-2</v>
+        <v>4.0008735509199998E-2</v>
       </c>
       <c r="I21" s="18" t="s">
         <v>13</v>
@@ -1642,16 +1636,16 @@
         <v>13</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F22" s="17">
-        <v>5692</v>
+        <v>6292</v>
       </c>
       <c r="G22" s="18">
-        <v>30.95</v>
+        <v>40.229999999999997</v>
       </c>
       <c r="H22" s="19">
-        <v>3.5482551902899999E-2</v>
+        <v>3.93533356855E-2</v>
       </c>
       <c r="I22" s="18" t="s">
         <v>13</v>
@@ -1671,16 +1665,16 @@
         <v>13</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="F23" s="17">
-        <v>6829</v>
+        <v>32174</v>
       </c>
       <c r="G23" s="18">
-        <v>30.72</v>
+        <v>36.92</v>
       </c>
       <c r="H23" s="19">
-        <v>3.5218868964599997E-2</v>
+        <v>3.61154649144E-2</v>
       </c>
       <c r="I23" s="18" t="s">
         <v>13</v>
@@ -1703,13 +1697,13 @@
         <v>59</v>
       </c>
       <c r="F24" s="17">
-        <v>15516</v>
+        <v>17141</v>
       </c>
       <c r="G24" s="18">
-        <v>27.48</v>
+        <v>32.53</v>
       </c>
       <c r="H24" s="19">
-        <v>3.1504378878500001E-2</v>
+        <v>3.1821128755899999E-2</v>
       </c>
       <c r="I24" s="18" t="s">
         <v>13</v>
@@ -1729,16 +1723,16 @@
         <v>13</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="F25" s="17">
-        <v>29124</v>
+        <v>7544</v>
       </c>
       <c r="G25" s="18">
-        <v>27.16</v>
+        <v>30.35</v>
       </c>
       <c r="H25" s="19">
-        <v>3.11375156601E-2</v>
+        <v>2.9688633806900001E-2</v>
       </c>
       <c r="I25" s="18" t="s">
         <v>13</v>
@@ -1758,16 +1752,16 @@
         <v>13</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F26" s="17">
-        <v>20519</v>
+        <v>17751</v>
       </c>
       <c r="G26" s="18">
-        <v>20.77</v>
+        <v>26.06</v>
       </c>
       <c r="H26" s="19">
-        <v>2.3811715768100001E-2</v>
+        <v>2.5492118517599999E-2</v>
       </c>
       <c r="I26" s="18" t="s">
         <v>13</v>
@@ -1787,16 +1781,16 @@
         <v>13</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F27" s="17">
-        <v>16068</v>
+        <v>22668</v>
       </c>
       <c r="G27" s="18">
-        <v>18.559999999999999</v>
+        <v>23.99</v>
       </c>
       <c r="H27" s="19">
-        <v>2.12780666661E-2</v>
+        <v>2.3467226524799999E-2</v>
       </c>
       <c r="I27" s="18" t="s">
         <v>13</v>
@@ -1816,16 +1810,16 @@
         <v>13</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F28" s="17">
-        <v>9898</v>
+        <v>10935</v>
       </c>
       <c r="G28" s="18">
-        <v>18.53</v>
+        <v>22.1</v>
       </c>
       <c r="H28" s="19">
-        <v>2.1243673239400001E-2</v>
+        <v>2.1618412096599999E-2</v>
       </c>
       <c r="I28" s="18" t="s">
         <v>13</v>
@@ -1848,13 +1842,13 @@
         <v>70</v>
       </c>
       <c r="F29" s="17">
-        <v>2397</v>
+        <v>2649</v>
       </c>
       <c r="G29" s="18">
-        <v>14.47</v>
+        <v>16.63</v>
       </c>
       <c r="H29" s="19">
-        <v>1.6589096156199998E-2</v>
+        <v>1.6267610550500002E-2</v>
       </c>
       <c r="I29" s="18" t="s">
         <v>13</v>
@@ -1874,16 +1868,16 @@
         <v>13</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="F30" s="17">
-        <v>4192</v>
+        <v>12001</v>
       </c>
       <c r="G30" s="18">
-        <v>13.26</v>
+        <v>15.5</v>
       </c>
       <c r="H30" s="19">
-        <v>1.52018946117E-2</v>
+        <v>1.51622347284E-2</v>
       </c>
       <c r="I30" s="18" t="s">
         <v>13</v>
@@ -1906,13 +1900,13 @@
         <v>75</v>
       </c>
       <c r="F31" s="17">
-        <v>19045</v>
+        <v>21039</v>
       </c>
       <c r="G31" s="18">
-        <v>12.59</v>
+        <v>14.97</v>
       </c>
       <c r="H31" s="19">
-        <v>1.44337747482E-2</v>
+        <v>1.4643784121599999E-2</v>
       </c>
       <c r="I31" s="18" t="s">
         <v>13</v>
@@ -1932,16 +1926,16 @@
         <v>13</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F32" s="17">
-        <v>2138</v>
+        <v>2360</v>
       </c>
       <c r="G32" s="18">
-        <v>11.88</v>
+        <v>14.55</v>
       </c>
       <c r="H32" s="19">
-        <v>1.36197969824E-2</v>
+        <v>1.4232936470899999E-2</v>
       </c>
       <c r="I32" s="18" t="s">
         <v>13</v>
@@ -1961,16 +1955,16 @@
         <v>13</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="F33" s="17">
-        <v>10864</v>
+        <v>4632</v>
       </c>
       <c r="G33" s="18">
-        <v>11.67</v>
+        <v>14.23</v>
       </c>
       <c r="H33" s="19">
-        <v>1.3379042995299999E-2</v>
+        <v>1.39199096894E-2</v>
       </c>
       <c r="I33" s="18" t="s">
         <v>13</v>
@@ -1990,16 +1984,16 @@
         <v>13</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="F34" s="17">
-        <v>1911</v>
+        <v>10681</v>
       </c>
       <c r="G34" s="18">
-        <v>11.43</v>
+        <v>13.02</v>
       </c>
       <c r="H34" s="19">
-        <v>1.31038955815E-2</v>
+        <v>1.27362771718E-2</v>
       </c>
       <c r="I34" s="18" t="s">
         <v>13</v>
@@ -2019,16 +2013,16 @@
         <v>13</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="F35" s="17">
-        <v>9668</v>
+        <v>2110</v>
       </c>
       <c r="G35" s="18">
-        <v>10.88</v>
+        <v>12.59</v>
       </c>
       <c r="H35" s="19">
-        <v>1.24733494249E-2</v>
+        <v>1.23156474342E-2</v>
       </c>
       <c r="I35" s="18" t="s">
         <v>13</v>
@@ -2048,16 +2042,16 @@
         <v>13</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="F36" s="17">
-        <v>619</v>
+        <v>3280</v>
       </c>
       <c r="G36" s="18">
-        <v>6.1</v>
+        <v>6.78</v>
       </c>
       <c r="H36" s="19">
-        <v>6.9933301003999998E-3</v>
+        <v>6.6322549328000002E-3</v>
       </c>
       <c r="I36" s="18" t="s">
         <v>13</v>
@@ -2068,25 +2062,25 @@
     </row>
     <row r="37" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B37" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C37" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="C37" s="16" t="s">
+      <c r="D37" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="D37" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E37" s="16" t="s">
-        <v>59</v>
-      </c>
       <c r="F37" s="17">
-        <v>2968</v>
+        <v>684</v>
       </c>
       <c r="G37" s="18">
-        <v>5.99</v>
+        <v>6.07</v>
       </c>
       <c r="H37" s="19">
-        <v>6.8672208689999998E-3</v>
+        <v>5.9377267613000004E-3</v>
       </c>
       <c r="I37" s="18" t="s">
         <v>13</v>
@@ -2601,10 +2595,10 @@
         <v>13</v>
       </c>
       <c r="G65" s="12">
-        <v>0.01</v>
-      </c>
-      <c r="H65" s="19" t="s">
-        <v>103</v>
+        <v>1.06</v>
+      </c>
+      <c r="H65" s="13">
+        <v>1.0369012135999999E-3</v>
       </c>
       <c r="I65" s="12" t="s">
         <v>13</v>
@@ -2623,7 +2617,7 @@
     </row>
     <row r="67" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B67" s="20" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C67" s="21" t="s">
         <v>13</v>
@@ -2638,10 +2632,10 @@
         <v>13</v>
       </c>
       <c r="G67" s="21">
-        <v>1.9896978000002719</v>
+        <v>-1.0332526999999345</v>
       </c>
       <c r="H67" s="22">
-        <v>2.281084182862807E-3</v>
+        <v>-1.0107367723357925E-3</v>
       </c>
       <c r="I67" s="21" t="s">
         <v>13</v>
@@ -2652,36 +2646,36 @@
     </row>
     <row r="68" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B68" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="C68" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D68" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="E68" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F68" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G68" s="21">
+        <v>1022.2767473</v>
+      </c>
+      <c r="H68" s="22">
+        <v>0.99999999999846434</v>
+      </c>
+      <c r="I68" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="J68" s="23" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="71" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B71" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="C68" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="D68" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="E68" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F68" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G68" s="21">
-        <v>872.25969780000003</v>
-      </c>
-      <c r="H68" s="22">
-        <v>0.99999999999826295</v>
-      </c>
-      <c r="I68" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="J68" s="23" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="71" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B71" s="6" t="s">
-        <v>106</v>
       </c>
       <c r="C71" s="5"/>
       <c r="D71" s="5"/>
@@ -2692,8 +2686,8 @@
       <c r="I71" s="5"/>
     </row>
     <row r="72" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B72" s="6" t="s">
-        <v>107</v>
+      <c r="B72" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="C72" s="5"/>
       <c r="D72" s="5"/>
@@ -2702,9 +2696,9 @@
       <c r="G72" s="5"/>
       <c r="H72" s="5"/>
     </row>
-    <row r="73" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B73" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C73" s="5"/>
       <c r="D73" s="5"/>
@@ -2714,8 +2708,8 @@
       <c r="H73" s="5"/>
     </row>
     <row r="74" spans="2:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B74" s="4" t="s">
-        <v>109</v>
+      <c r="B74" s="6" t="s">
+        <v>108</v>
       </c>
       <c r="C74" s="5"/>
       <c r="D74" s="5"/>
@@ -2725,8 +2719,8 @@
       <c r="H74" s="5"/>
     </row>
     <row r="75" spans="2:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B75" s="4" t="s">
-        <v>110</v>
+      <c r="B75" s="6" t="s">
+        <v>109</v>
       </c>
       <c r="C75" s="5"/>
       <c r="D75" s="5"/>
@@ -2735,38 +2729,26 @@
       <c r="G75" s="5"/>
       <c r="H75" s="5"/>
     </row>
-    <row r="76" spans="2:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B76" s="4" t="s">
+    <row r="78" spans="2:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B78" s="24" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="93" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B93" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="C76" s="5"/>
-      <c r="D76" s="5"/>
-      <c r="E76" s="5"/>
-      <c r="F76" s="5"/>
-      <c r="G76" s="5"/>
-      <c r="H76" s="5"/>
-    </row>
-    <row r="79" spans="2:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B79" s="24" t="s">
+    </row>
+    <row r="94" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B94" s="24" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="94" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B94" s="24" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="95" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B95" s="24" t="s">
-        <v>114</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="B73:H73"/>
     <mergeCell ref="B74:H74"/>
     <mergeCell ref="B75:H75"/>
-    <mergeCell ref="B76:H76"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
